--- a/dnis.xlsx
+++ b/dnis.xlsx
@@ -435,7 +435,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15161414</v>
+        <v>60069778</v>
       </c>
     </row>
   </sheetData>
